--- a/backend/templates/testify.xlsx
+++ b/backend/templates/testify.xlsx
@@ -1641,8 +1641,10 @@
       <c r="F14" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="57" t="s">
-        <v>27</v>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">투입 인력</t>
+        </is>
       </c>
       <c r="H14" s="99" t="s">
         <v>21</v>
@@ -2791,8 +2793,10 @@
       <c r="F14" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="57" t="s">
-        <v>27</v>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">투입 인력</t>
+        </is>
       </c>
       <c r="H14" s="99" t="s">
         <v>21</v>

--- a/backend/templates/testify.xlsx
+++ b/backend/templates/testify.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a111-04-2310-01/Desktop/데이터전략본부 자료/데본 AX 자료/데솔 AX/견적서 자동화 솔루션/견적서-시장검증/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB2A3238-68BF-E44C-84C9-CA3A04807098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275CB330-0FE9-2C41-95B0-53AC88D8E881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35600" yWindow="-5360" windowWidth="46300" windowHeight="25420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시장검증" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">마케팅!$A$1:$K$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">시장검증!$A$1:$K$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">시장검증!$A$1:$K$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>비고</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -162,10 +162,54 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>시장성 테스트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BM 진단 및 고도화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 리포트 제공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>㈜미구 귀하</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>설문형 시장검증</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문 설계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설문 데이터 가공 및 시각화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MVP 광고안 기획 및 제작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">설문응답자 모집 및 운영
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>*설문응답 리워드 포함</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>3월</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -174,6 +218,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>정량 데이터 시계열 분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정량 데이터 클러스터 분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용역명: 정량, 정성 데이터 기반 시장 검증 용역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>온라인 광고</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -239,30 +295,6 @@
   </si>
   <si>
     <t>용역명: 그로스해킹 마케팅 대행 용역</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>년</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>월</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>일</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 귀하</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">용역명: </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼드체로 작성</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -275,7 +307,7 @@
     <numFmt numFmtId="177" formatCode="#&quot;명&quot;"/>
     <numFmt numFmtId="178" formatCode="#0.0&quot;개월&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <name val="바탕체"/>
@@ -398,6 +430,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -614,7 +652,7 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -771,7 +809,40 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -843,12 +914,6 @@
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -856,15 +921,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1014,14 +1070,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>555274</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>308848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>441985</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>99603</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>99602</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1393,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U179"/>
+  <dimension ref="A1:U196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="2.1640625" style="6" customWidth="1"/>
@@ -1447,39 +1503,39 @@
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="84"/>
-      <c r="H3" s="100" t="s">
+      <c r="G3" s="93"/>
+      <c r="H3" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="89"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="13"/>
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A4" s="11"/>
       <c r="B4" s="16" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="84" t="s">
+      <c r="F4" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="97" t="s">
+      <c r="G4" s="93"/>
+      <c r="H4" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="104"/>
       <c r="K4" s="13"/>
       <c r="P4" s="15"/>
     </row>
@@ -1489,34 +1545,34 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="84" t="s">
+      <c r="F5" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="84"/>
-      <c r="H5" s="97" t="s">
+      <c r="G5" s="93"/>
+      <c r="H5" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="97"/>
-      <c r="J5" s="98"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="104"/>
       <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:16" s="14" customFormat="1" ht="40" customHeight="1">
       <c r="A6" s="11"/>
-      <c r="B6" s="106" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="84" t="s">
+      <c r="B6" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="84"/>
-      <c r="H6" s="97" t="s">
+      <c r="G6" s="93"/>
+      <c r="H6" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="97"/>
-      <c r="J6" s="98"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
       <c r="K6" s="13"/>
     </row>
     <row r="7" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1">
@@ -1527,15 +1583,15 @@
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="84" t="s">
+      <c r="F7" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="84"/>
-      <c r="H7" s="105" t="s">
+      <c r="G7" s="93"/>
+      <c r="H7" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="108"/>
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1">
@@ -1543,15 +1599,15 @@
       <c r="C8" s="19"/>
       <c r="D8" s="20"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="84" t="s">
+      <c r="F8" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="84"/>
-      <c r="H8" s="101" t="s">
+      <c r="G8" s="93"/>
+      <c r="H8" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="101"/>
-      <c r="J8" s="102"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="108"/>
       <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:16" s="14" customFormat="1" ht="20" customHeight="1">
@@ -1569,19 +1625,19 @@
     </row>
     <row r="10" spans="1:16" s="14" customFormat="1" ht="22" customHeight="1" thickBot="1">
       <c r="A10" s="11"/>
-      <c r="B10" s="104"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
       <c r="G10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="86">
-        <f>H28</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="86"/>
+      <c r="H10" s="95">
+        <f>H45</f>
+        <v>19800000</v>
+      </c>
+      <c r="I10" s="95"/>
       <c r="J10" s="26" t="s">
         <v>2</v>
       </c>
@@ -1602,533 +1658,724 @@
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" ht="22" customHeight="1">
       <c r="A12" s="11"/>
-      <c r="B12" s="103" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
+      <c r="B12" s="109" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="109"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:16" s="14" customFormat="1" ht="22" customHeight="1">
       <c r="A13" s="11"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
       <c r="I13" s="29"/>
       <c r="J13" s="30"/>
       <c r="K13" s="31"/>
     </row>
     <row r="14" spans="1:16" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
       <c r="E14" s="32" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">투입 인력</t>
-        </is>
-      </c>
-      <c r="H14" s="99" t="s">
+      <c r="G14" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99" t="s">
+      <c r="I14" s="105"/>
+      <c r="J14" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="K14" s="99"/>
+      <c r="K14" s="105"/>
     </row>
     <row r="15" spans="1:16" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="96"/>
+      <c r="A15" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="102"/>
       <c r="E15" s="33"/>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="93">
+      <c r="H15" s="99">
         <f>SUM(H16:I20)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="93"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="83"/>
+        <v>9000000</v>
+      </c>
+      <c r="I15" s="99"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="69"/>
     </row>
     <row r="16" spans="1:16" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A16" s="87"/>
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="92">
+      <c r="A16" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="33">
+        <v>500000</v>
+      </c>
+      <c r="F16" s="34">
+        <v>1</v>
+      </c>
+      <c r="G16" s="35">
+        <v>1</v>
+      </c>
+      <c r="H16" s="98">
         <f>E16</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="92"/>
+        <v>500000</v>
+      </c>
+      <c r="I16" s="98"/>
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
-    <row r="17" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="87"/>
-      <c r="B17" s="88"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="92">
+    <row r="17" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A17" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="33">
+        <v>2000000</v>
+      </c>
+      <c r="F17" s="34">
+        <v>1</v>
+      </c>
+      <c r="G17" s="35">
+        <v>2</v>
+      </c>
+      <c r="H17" s="98">
         <f>E17*F17*G17</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="92"/>
+        <v>4000000</v>
+      </c>
+      <c r="I17" s="98"/>
       <c r="J17" s="36"/>
       <c r="K17" s="37"/>
     </row>
-    <row r="18" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="92">
+    <row r="18" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A18" s="96" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="33">
+        <v>2000000</v>
+      </c>
+      <c r="F18" s="34">
+        <v>1</v>
+      </c>
+      <c r="G18" s="35">
+        <v>1</v>
+      </c>
+      <c r="H18" s="98">
         <f>E18*F18*G18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="92"/>
+        <v>2000000</v>
+      </c>
+      <c r="I18" s="98"/>
       <c r="J18" s="36"/>
       <c r="K18" s="37"/>
     </row>
-    <row r="19" spans="1:21" s="14" customFormat="1" ht="27" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="92">
+    <row r="19" spans="1:11" s="14" customFormat="1" ht="27" customHeight="1">
+      <c r="A19" s="96" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="33">
+        <v>2000000</v>
+      </c>
+      <c r="F19" s="34">
+        <v>1</v>
+      </c>
+      <c r="G19" s="35">
+        <v>1</v>
+      </c>
+      <c r="H19" s="98">
         <f>E19*F19*G19</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="92"/>
+        <v>2000000</v>
+      </c>
+      <c r="I19" s="98"/>
       <c r="J19" s="36"/>
       <c r="K19" s="37"/>
     </row>
-    <row r="20" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A20" s="87"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="92"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="83"/>
-    </row>
-    <row r="21" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A21" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="96"/>
+    <row r="20" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A20" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="33">
+        <v>700000</v>
+      </c>
+      <c r="F20" s="34">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35">
+        <v>1</v>
+      </c>
+      <c r="H20" s="98">
+        <v>500000</v>
+      </c>
+      <c r="I20" s="98"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
+    </row>
+    <row r="21" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A21" s="100" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="101"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="102"/>
       <c r="E21" s="33"/>
       <c r="F21" s="34"/>
       <c r="G21" s="35"/>
-      <c r="H21" s="93">
-        <f>SUM(H22:I25)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="93"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="83"/>
-    </row>
-    <row r="22" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A22" s="87"/>
-      <c r="B22" s="88"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="92">
+      <c r="H21" s="99">
+        <f>SUM(H22:I42)</f>
+        <v>9000000</v>
+      </c>
+      <c r="I21" s="99"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="69"/>
+    </row>
+    <row r="22" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A22" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="33">
+        <v>500000</v>
+      </c>
+      <c r="F22" s="34">
+        <v>1</v>
+      </c>
+      <c r="G22" s="35">
+        <v>1</v>
+      </c>
+      <c r="H22" s="98">
         <f>E22</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="92"/>
+        <v>500000</v>
+      </c>
+      <c r="I22" s="98"/>
       <c r="J22" s="36"/>
       <c r="K22" s="37"/>
     </row>
-    <row r="23" spans="1:21" s="14" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A23" s="90"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="92">
-        <f t="shared" ref="H23:H25" si="0">E23</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="92"/>
+    <row r="23" spans="1:11" s="14" customFormat="1" ht="30.5" customHeight="1">
+      <c r="A23" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="33">
+        <v>4000000</v>
+      </c>
+      <c r="F23" s="34">
+        <v>1</v>
+      </c>
+      <c r="G23" s="35">
+        <v>1</v>
+      </c>
+      <c r="H23" s="98">
+        <f t="shared" ref="H23" si="0">E23</f>
+        <v>4000000</v>
+      </c>
+      <c r="I23" s="98"/>
       <c r="J23" s="36"/>
       <c r="K23" s="37"/>
     </row>
-    <row r="24" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="87"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="92">
+    <row r="24" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A24" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="33">
+        <v>3500000</v>
+      </c>
+      <c r="F24" s="34">
+        <v>1</v>
+      </c>
+      <c r="G24" s="35">
+        <v>1</v>
+      </c>
+      <c r="H24" s="98">
         <f>E24*F24*G24</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="92"/>
+        <v>3500000</v>
+      </c>
+      <c r="I24" s="98"/>
       <c r="J24" s="36"/>
       <c r="K24" s="37"/>
     </row>
-    <row r="25" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="92">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="92"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="83"/>
-    </row>
-    <row r="26" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="65" t="s">
+    <row r="25" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A25" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="33">
+        <v>1000000</v>
+      </c>
+      <c r="F25" s="34">
+        <v>1</v>
+      </c>
+      <c r="G25" s="35">
+        <v>1</v>
+      </c>
+      <c r="H25" s="98">
+        <f t="shared" ref="H25" si="1">E25</f>
+        <v>1000000</v>
+      </c>
+      <c r="I25" s="98"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="69"/>
+    </row>
+    <row r="26" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A26" s="58"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="37"/>
+    </row>
+    <row r="27" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A27" s="63"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="69"/>
+    </row>
+    <row r="28" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A28" s="58"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="37"/>
+    </row>
+    <row r="29" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A29" s="58"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="37"/>
+    </row>
+    <row r="30" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A30" s="58"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="37"/>
+    </row>
+    <row r="31" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A31" s="58"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="37"/>
+    </row>
+    <row r="32" spans="1:11" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A32" s="58"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="37"/>
+    </row>
+    <row r="33" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A33" s="58"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="37"/>
+    </row>
+    <row r="34" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A34" s="58"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="37"/>
+    </row>
+    <row r="35" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A35" s="58"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="37"/>
+    </row>
+    <row r="36" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A36" s="58"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="37"/>
+    </row>
+    <row r="37" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A37" s="58"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="62"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="37"/>
+    </row>
+    <row r="38" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A38" s="58"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="37"/>
+    </row>
+    <row r="39" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A39" s="58"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="37"/>
+    </row>
+    <row r="40" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A40" s="58"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="37"/>
+    </row>
+    <row r="41" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A41" s="58"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="37"/>
+    </row>
+    <row r="42" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A42" s="63"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="68"/>
+      <c r="K42" s="69"/>
+    </row>
+    <row r="43" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A43" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="64">
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="75">
         <f>H15+H21</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="15"/>
-      <c r="U26" s="38"/>
-    </row>
-    <row r="27" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A27" s="77" t="s">
+        <v>18000000</v>
+      </c>
+      <c r="I43" s="75"/>
+      <c r="J43" s="91"/>
+      <c r="K43" s="92"/>
+      <c r="L43" s="15"/>
+      <c r="U43" s="38"/>
+    </row>
+    <row r="44" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A44" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="62">
-        <f>H26*0.1</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="63"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="15"/>
-      <c r="P27" s="41"/>
-    </row>
-    <row r="28" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A28" s="66" t="s">
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="73">
+        <f>H43*0.1</f>
+        <v>1800000</v>
+      </c>
+      <c r="I44" s="74"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="15"/>
+      <c r="P44" s="41"/>
+    </row>
+    <row r="45" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
+      <c r="A45" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="60">
-        <f>SUM(H27,H26)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="61"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="43"/>
-    </row>
-    <row r="29" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A29" s="68" t="s">
+      <c r="B45" s="78"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="78"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="71">
+        <f>SUM(H44,H43)</f>
+        <v>19800000</v>
+      </c>
+      <c r="I45" s="72"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
+      <c r="A46" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="1" t="s">
+      <c r="B46" s="80"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="47"/>
-    </row>
-    <row r="30" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A30" s="71"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="1" t="s">
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="47"/>
+    </row>
+    <row r="47" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
+      <c r="A47" s="82"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="84"/>
+      <c r="D47" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="44"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="18"/>
-    </row>
-    <row r="31" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A31" s="74"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="2" t="s">
+      <c r="E47" s="44"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="18"/>
+    </row>
+    <row r="48" spans="1:21" s="14" customFormat="1" ht="22" customHeight="1">
+      <c r="A48" s="85"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="87"/>
+      <c r="D48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="31"/>
-    </row>
-    <row r="32" spans="1:21" s="14" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="18"/>
-    </row>
-    <row r="33" spans="1:11" s="14" customFormat="1" ht="28" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="E33" s="59" t="s">
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="31"/>
+    </row>
+    <row r="49" spans="1:11" s="14" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A49" s="11"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="18"/>
+    </row>
+    <row r="50" spans="1:11" s="14" customFormat="1" ht="28" customHeight="1">
+      <c r="A50" s="11"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="48"/>
+      <c r="E50" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="52" t="s">
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="18"/>
-    </row>
-    <row r="34" spans="1:11" s="14" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A34" s="53"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="31"/>
-    </row>
-    <row r="35" spans="1:11" s="14" customFormat="1" ht="20" customHeight="1"/>
-    <row r="36" spans="1:11" s="14" customFormat="1" ht="20" customHeight="1"/>
-    <row r="37" spans="1:11" s="14" customFormat="1" ht="20" customHeight="1"/>
-    <row r="38" spans="1:11" s="14" customFormat="1" ht="25.5" customHeight="1"/>
-    <row r="39" spans="1:11" s="14" customFormat="1" ht="27.75" customHeight="1"/>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E40" s="56"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E41" s="56"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E42" s="56"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E43" s="56"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E44" s="56"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E45" s="56"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E46" s="56"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E47" s="56"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:11" s="14" customFormat="1" ht="15">
-      <c r="E48" s="56"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E49" s="56"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-    </row>
-    <row r="50" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E50" s="56"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E51" s="56"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-    </row>
-    <row r="52" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E52" s="56"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="53" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E53" s="56"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-    </row>
-    <row r="54" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E54" s="56"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-    </row>
-    <row r="55" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E55" s="56"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-    </row>
-    <row r="56" spans="5:10" s="14" customFormat="1" ht="15">
-      <c r="E56" s="56"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-    </row>
-    <row r="57" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="18"/>
+    </row>
+    <row r="51" spans="1:11" s="14" customFormat="1" ht="30.75" customHeight="1">
+      <c r="A51" s="53"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="31"/>
+    </row>
+    <row r="52" spans="1:11" s="14" customFormat="1" ht="20" customHeight="1"/>
+    <row r="53" spans="1:11" s="14" customFormat="1" ht="20" customHeight="1"/>
+    <row r="54" spans="1:11" s="14" customFormat="1" ht="20" customHeight="1"/>
+    <row r="55" spans="1:11" s="14" customFormat="1" ht="25.5" customHeight="1"/>
+    <row r="56" spans="1:11" s="14" customFormat="1" ht="27.75" customHeight="1"/>
+    <row r="57" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E57" s="56"/>
       <c r="H57" s="15"/>
       <c r="I57" s="15"/>
       <c r="J57" s="15"/>
     </row>
-    <row r="58" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="58" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E58" s="56"/>
       <c r="H58" s="15"/>
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
     </row>
-    <row r="59" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="59" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E59" s="56"/>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
       <c r="J59" s="15"/>
     </row>
-    <row r="60" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="60" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E60" s="56"/>
       <c r="H60" s="15"/>
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
     </row>
-    <row r="61" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="61" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E61" s="56"/>
       <c r="H61" s="15"/>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
     </row>
-    <row r="62" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="62" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E62" s="56"/>
       <c r="H62" s="15"/>
       <c r="I62" s="15"/>
       <c r="J62" s="15"/>
     </row>
-    <row r="63" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="63" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E63" s="56"/>
       <c r="H63" s="15"/>
       <c r="I63" s="15"/>
       <c r="J63" s="15"/>
     </row>
-    <row r="64" spans="5:10" s="14" customFormat="1" ht="15">
+    <row r="64" spans="1:11" s="14" customFormat="1" ht="15">
       <c r="E64" s="56"/>
       <c r="H64" s="15"/>
       <c r="I64" s="15"/>
@@ -2326,118 +2573,203 @@
       <c r="I96" s="15"/>
       <c r="J96" s="15"/>
     </row>
-    <row r="97" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="97" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E97" s="56"/>
       <c r="H97" s="15"/>
       <c r="I97" s="15"/>
       <c r="J97" s="15"/>
     </row>
-    <row r="98" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="98" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E98" s="56"/>
       <c r="H98" s="15"/>
       <c r="I98" s="15"/>
       <c r="J98" s="15"/>
     </row>
-    <row r="99" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="99" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E99" s="56"/>
       <c r="H99" s="15"/>
       <c r="I99" s="15"/>
       <c r="J99" s="15"/>
     </row>
-    <row r="100" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="100" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E100" s="56"/>
       <c r="H100" s="15"/>
       <c r="I100" s="15"/>
       <c r="J100" s="15"/>
     </row>
-    <row r="101" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="101" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E101" s="56"/>
       <c r="H101" s="15"/>
       <c r="I101" s="15"/>
       <c r="J101" s="15"/>
     </row>
-    <row r="102" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="102" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E102" s="56"/>
       <c r="H102" s="15"/>
       <c r="I102" s="15"/>
       <c r="J102" s="15"/>
     </row>
-    <row r="103" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="103" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E103" s="56"/>
       <c r="H103" s="15"/>
       <c r="I103" s="15"/>
       <c r="J103" s="15"/>
     </row>
-    <row r="104" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="104" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E104" s="56"/>
       <c r="H104" s="15"/>
       <c r="I104" s="15"/>
       <c r="J104" s="15"/>
     </row>
-    <row r="105" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="105" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E105" s="56"/>
       <c r="H105" s="15"/>
       <c r="I105" s="15"/>
       <c r="J105" s="15"/>
     </row>
-    <row r="106" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="106" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E106" s="56"/>
       <c r="H106" s="15"/>
       <c r="I106" s="15"/>
       <c r="J106" s="15"/>
     </row>
-    <row r="107" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="107" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E107" s="56"/>
       <c r="H107" s="15"/>
       <c r="I107" s="15"/>
       <c r="J107" s="15"/>
     </row>
-    <row r="108" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="108" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E108" s="56"/>
       <c r="H108" s="15"/>
       <c r="I108" s="15"/>
       <c r="J108" s="15"/>
     </row>
-    <row r="109" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="109" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E109" s="56"/>
       <c r="H109" s="15"/>
       <c r="I109" s="15"/>
       <c r="J109" s="15"/>
     </row>
-    <row r="110" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="110" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E110" s="56"/>
       <c r="H110" s="15"/>
       <c r="I110" s="15"/>
       <c r="J110" s="15"/>
     </row>
-    <row r="111" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="111" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E111" s="56"/>
       <c r="H111" s="15"/>
       <c r="I111" s="15"/>
       <c r="J111" s="15"/>
     </row>
-    <row r="112" spans="8:10" s="14" customFormat="1" ht="15">
+    <row r="112" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E112" s="56"/>
       <c r="H112" s="15"/>
       <c r="I112" s="15"/>
       <c r="J112" s="15"/>
     </row>
-    <row r="113" s="14" customFormat="1" ht="15"/>
-    <row r="114" s="14" customFormat="1" ht="15"/>
-    <row r="115" s="14" customFormat="1" ht="15"/>
-    <row r="116" s="14" customFormat="1" ht="15"/>
-    <row r="117" s="14" customFormat="1" ht="15"/>
-    <row r="118" s="14" customFormat="1" ht="15"/>
-    <row r="119" s="14" customFormat="1" ht="15"/>
-    <row r="120" s="14" customFormat="1" ht="15"/>
-    <row r="121" s="14" customFormat="1" ht="15"/>
-    <row r="122" s="14" customFormat="1" ht="15"/>
-    <row r="123" s="14" customFormat="1" ht="15"/>
-    <row r="124" s="14" customFormat="1" ht="15"/>
-    <row r="125" s="14" customFormat="1" ht="15"/>
-    <row r="126" s="14" customFormat="1" ht="15"/>
-    <row r="127" s="14" customFormat="1" ht="15"/>
-    <row r="128" s="14" customFormat="1" ht="15"/>
-    <row r="129" s="14" customFormat="1" ht="15"/>
-    <row r="130" s="14" customFormat="1" ht="15"/>
-    <row r="131" s="14" customFormat="1" ht="15"/>
-    <row r="132" s="14" customFormat="1" ht="15"/>
-    <row r="133" s="14" customFormat="1" ht="15"/>
-    <row r="134" s="14" customFormat="1" ht="15"/>
-    <row r="135" s="14" customFormat="1" ht="15"/>
-    <row r="136" s="14" customFormat="1" ht="15"/>
-    <row r="137" s="14" customFormat="1" ht="15"/>
-    <row r="138" s="14" customFormat="1" ht="15"/>
-    <row r="139" s="14" customFormat="1" ht="15"/>
-    <row r="140" s="14" customFormat="1" ht="15"/>
-    <row r="141" s="14" customFormat="1" ht="15"/>
-    <row r="142" s="14" customFormat="1" ht="15"/>
-    <row r="143" s="14" customFormat="1" ht="15"/>
-    <row r="144" s="14" customFormat="1" ht="15"/>
+    <row r="113" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="E113" s="56"/>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="15"/>
+    </row>
+    <row r="114" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+      <c r="J114" s="15"/>
+    </row>
+    <row r="115" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+      <c r="J115" s="15"/>
+    </row>
+    <row r="116" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
+      <c r="J116" s="15"/>
+    </row>
+    <row r="117" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H117" s="15"/>
+      <c r="I117" s="15"/>
+      <c r="J117" s="15"/>
+    </row>
+    <row r="118" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H118" s="15"/>
+      <c r="I118" s="15"/>
+      <c r="J118" s="15"/>
+    </row>
+    <row r="119" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="15"/>
+    </row>
+    <row r="120" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="15"/>
+    </row>
+    <row r="121" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H121" s="15"/>
+      <c r="I121" s="15"/>
+      <c r="J121" s="15"/>
+    </row>
+    <row r="122" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
+      <c r="J122" s="15"/>
+    </row>
+    <row r="123" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
+      <c r="J123" s="15"/>
+    </row>
+    <row r="124" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
+      <c r="J124" s="15"/>
+    </row>
+    <row r="125" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
+      <c r="J125" s="15"/>
+    </row>
+    <row r="126" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+      <c r="J126" s="15"/>
+    </row>
+    <row r="127" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H127" s="15"/>
+      <c r="I127" s="15"/>
+      <c r="J127" s="15"/>
+    </row>
+    <row r="128" spans="5:10" s="14" customFormat="1" ht="15">
+      <c r="H128" s="15"/>
+      <c r="I128" s="15"/>
+      <c r="J128" s="15"/>
+    </row>
+    <row r="129" spans="8:10" s="14" customFormat="1" ht="15">
+      <c r="H129" s="15"/>
+      <c r="I129" s="15"/>
+      <c r="J129" s="15"/>
+    </row>
+    <row r="130" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="131" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="132" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="133" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="134" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="135" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="136" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="137" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="138" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="139" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="140" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="141" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="142" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="143" spans="8:10" s="14" customFormat="1" ht="15"/>
+    <row r="144" spans="8:10" s="14" customFormat="1" ht="15"/>
     <row r="145" s="14" customFormat="1" ht="15"/>
     <row r="146" s="14" customFormat="1" ht="15"/>
     <row r="147" s="14" customFormat="1" ht="15"/>
@@ -2473,26 +2805,26 @@
     <row r="177" s="14" customFormat="1" ht="15"/>
     <row r="178" s="14" customFormat="1" ht="15"/>
     <row r="179" s="14" customFormat="1" ht="15"/>
+    <row r="180" s="14" customFormat="1" ht="15"/>
+    <row r="181" s="14" customFormat="1" ht="15"/>
+    <row r="182" s="14" customFormat="1" ht="15"/>
+    <row r="183" s="14" customFormat="1" ht="15"/>
+    <row r="184" s="14" customFormat="1" ht="15"/>
+    <row r="185" s="14" customFormat="1" ht="15"/>
+    <row r="186" s="14" customFormat="1" ht="15"/>
+    <row r="187" s="14" customFormat="1" ht="15"/>
+    <row r="188" s="14" customFormat="1" ht="15"/>
+    <row r="189" s="14" customFormat="1" ht="15"/>
+    <row r="190" s="14" customFormat="1" ht="15"/>
+    <row r="191" s="14" customFormat="1" ht="15"/>
+    <row r="192" s="14" customFormat="1" ht="15"/>
+    <row r="193" s="14" customFormat="1" ht="15"/>
+    <row r="194" s="14" customFormat="1" ht="15"/>
+    <row r="195" s="14" customFormat="1" ht="15"/>
+    <row r="196" s="14" customFormat="1" ht="15"/>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="A18:D18"/>
+  <mergeCells count="61">
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J14:K14"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H14:I14"/>
@@ -2506,8 +2838,23 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="H25:I25"/>
     <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J20:K20"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="H10:I10"/>
@@ -2516,20 +2863,28 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="H22:I22"/>
     <mergeCell ref="H23:I23"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:C31"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:C48"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -2599,15 +2954,15 @@
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="84"/>
-      <c r="H3" s="100" t="s">
+      <c r="G3" s="93"/>
+      <c r="H3" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="89"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="K3" s="13"/>
       <c r="P3" s="15"/>
     </row>
@@ -2617,21 +2972,21 @@
         <v>30</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="84" t="s">
+      <c r="F4" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="97" t="s">
+      <c r="G4" s="93"/>
+      <c r="H4" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="104"/>
       <c r="K4" s="13"/>
       <c r="P4" s="15"/>
     </row>
@@ -2641,34 +2996,34 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="84" t="s">
+      <c r="F5" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="84"/>
-      <c r="H5" s="97" t="s">
+      <c r="G5" s="93"/>
+      <c r="H5" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="97"/>
-      <c r="J5" s="98"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="104"/>
       <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:16" s="14" customFormat="1" ht="40" customHeight="1">
       <c r="A6" s="11"/>
-      <c r="B6" s="106" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="84" t="s">
+      <c r="B6" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="84"/>
-      <c r="H6" s="97" t="s">
+      <c r="G6" s="93"/>
+      <c r="H6" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="97"/>
-      <c r="J6" s="98"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
       <c r="K6" s="13"/>
     </row>
     <row r="7" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1">
@@ -2679,15 +3034,15 @@
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="84" t="s">
+      <c r="F7" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="84"/>
-      <c r="H7" s="105" t="s">
+      <c r="G7" s="93"/>
+      <c r="H7" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="108"/>
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1">
@@ -2695,15 +3050,15 @@
       <c r="C8" s="19"/>
       <c r="D8" s="20"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="84" t="s">
+      <c r="F8" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="84"/>
-      <c r="H8" s="101" t="s">
+      <c r="G8" s="93"/>
+      <c r="H8" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="101"/>
-      <c r="J8" s="102"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="108"/>
       <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:16" s="14" customFormat="1" ht="20" customHeight="1">
@@ -2721,19 +3076,19 @@
     </row>
     <row r="10" spans="1:16" s="14" customFormat="1" ht="22" customHeight="1" thickBot="1">
       <c r="A10" s="11"/>
-      <c r="B10" s="104"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
       <c r="G10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="86">
+      <c r="H10" s="95">
         <f>H33</f>
         <v>19800000</v>
       </c>
-      <c r="I10" s="86"/>
+      <c r="I10" s="95"/>
       <c r="J10" s="26" t="s">
         <v>2</v>
       </c>
@@ -2754,483 +3109,481 @@
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" ht="22" customHeight="1">
       <c r="A12" s="11"/>
-      <c r="B12" s="103" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
+      <c r="B12" s="109" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="109"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:16" s="14" customFormat="1" ht="22" customHeight="1">
       <c r="A13" s="11"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
       <c r="I13" s="29"/>
       <c r="J13" s="30"/>
       <c r="K13" s="31"/>
     </row>
     <row r="14" spans="1:16" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
       <c r="E14" s="32" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">투입 인력</t>
-        </is>
-      </c>
-      <c r="H14" s="99" t="s">
+      <c r="G14" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99" t="s">
+      <c r="I14" s="105"/>
+      <c r="J14" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="K14" s="99"/>
+      <c r="K14" s="105"/>
     </row>
     <row r="15" spans="1:16" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="96"/>
+      <c r="A15" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="102"/>
       <c r="E15" s="33"/>
       <c r="F15" s="34"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="93">
+      <c r="H15" s="99">
         <f>SUM(H16:I19)</f>
         <v>8000000</v>
       </c>
-      <c r="I15" s="93"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="83"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="69"/>
     </row>
     <row r="16" spans="1:16" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A16" s="87" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="89"/>
+      <c r="A16" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="65"/>
       <c r="E16" s="33">
         <v>500000</v>
       </c>
       <c r="F16" s="34">
         <v>1</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="61">
         <v>1</v>
       </c>
-      <c r="H16" s="92">
+      <c r="H16" s="98">
         <f>E16</f>
         <v>500000</v>
       </c>
-      <c r="I16" s="92"/>
+      <c r="I16" s="98"/>
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="87" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="88"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="89"/>
+      <c r="A17" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="65"/>
       <c r="E17" s="33">
         <v>500000</v>
       </c>
       <c r="F17" s="34">
         <v>1</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="61">
         <v>1</v>
       </c>
-      <c r="H17" s="92">
+      <c r="H17" s="98">
         <f>E17*F17*G17</f>
         <v>500000</v>
       </c>
-      <c r="I17" s="92"/>
+      <c r="I17" s="98"/>
       <c r="J17" s="36"/>
       <c r="K17" s="37"/>
     </row>
     <row r="18" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A18" s="90" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="89"/>
+      <c r="A18" s="96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
       <c r="E18" s="33">
         <v>200000</v>
       </c>
       <c r="F18" s="34">
         <v>1</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="61">
         <v>20</v>
       </c>
-      <c r="H18" s="92">
+      <c r="H18" s="98">
         <f>E18*F18*G18</f>
         <v>4000000</v>
       </c>
-      <c r="I18" s="92"/>
+      <c r="I18" s="98"/>
       <c r="J18" s="36"/>
       <c r="K18" s="37"/>
     </row>
     <row r="19" spans="1:21" s="14" customFormat="1" ht="27" customHeight="1">
-      <c r="A19" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="89"/>
+      <c r="A19" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="65"/>
       <c r="E19" s="33">
         <v>1000000</v>
       </c>
       <c r="F19" s="34">
         <v>3</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="61">
         <v>1</v>
       </c>
-      <c r="H19" s="92">
+      <c r="H19" s="98">
         <f>E19*F19*G19</f>
         <v>3000000</v>
       </c>
-      <c r="I19" s="92"/>
+      <c r="I19" s="98"/>
       <c r="J19" s="36"/>
       <c r="K19" s="37"/>
     </row>
     <row r="20" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A20" s="94" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="96"/>
+      <c r="A20" s="100" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="102"/>
       <c r="E20" s="33"/>
       <c r="F20" s="34"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="93">
+      <c r="G20" s="61"/>
+      <c r="H20" s="99">
         <f>SUM(H21:I23)</f>
         <v>2200000</v>
       </c>
-      <c r="I20" s="93"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="83"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="69"/>
     </row>
     <row r="21" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A21" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="89"/>
+      <c r="A21" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="33">
         <v>500000</v>
       </c>
       <c r="F21" s="34">
         <v>1</v>
       </c>
-      <c r="G21" s="58">
+      <c r="G21" s="61">
         <v>1</v>
       </c>
-      <c r="H21" s="92">
+      <c r="H21" s="98">
         <f>E21</f>
         <v>500000</v>
       </c>
-      <c r="I21" s="92"/>
+      <c r="I21" s="98"/>
       <c r="J21" s="36"/>
       <c r="K21" s="37"/>
     </row>
     <row r="22" spans="1:21" s="14" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A22" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
+      <c r="A22" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="65"/>
       <c r="E22" s="33">
         <v>1500000</v>
       </c>
       <c r="F22" s="34">
         <v>1</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G22" s="61">
         <v>1</v>
       </c>
-      <c r="H22" s="92">
+      <c r="H22" s="98">
         <f t="shared" ref="H22" si="0">E22</f>
         <v>1500000</v>
       </c>
-      <c r="I22" s="92"/>
+      <c r="I22" s="98"/>
       <c r="J22" s="36"/>
       <c r="K22" s="37"/>
     </row>
     <row r="23" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A23" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="89"/>
+      <c r="A23" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="33">
         <v>200000</v>
       </c>
       <c r="F23" s="34">
         <v>1</v>
       </c>
-      <c r="G23" s="58">
+      <c r="G23" s="61">
         <v>1</v>
       </c>
-      <c r="H23" s="92">
+      <c r="H23" s="98">
         <f>E23*F23*G23</f>
         <v>200000</v>
       </c>
-      <c r="I23" s="92"/>
+      <c r="I23" s="98"/>
       <c r="J23" s="36"/>
       <c r="K23" s="37"/>
     </row>
     <row r="24" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="95"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="96"/>
+      <c r="A24" s="100" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="102"/>
       <c r="E24" s="33"/>
       <c r="F24" s="34"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="93">
+      <c r="G24" s="61"/>
+      <c r="H24" s="99">
         <f>SUM(H25:I27)</f>
         <v>3000000</v>
       </c>
-      <c r="I24" s="93"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="83"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="69"/>
     </row>
     <row r="25" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A25" s="87" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="89"/>
+      <c r="A25" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="65"/>
       <c r="E25" s="33">
         <v>500000</v>
       </c>
       <c r="F25" s="34">
         <v>1</v>
       </c>
-      <c r="G25" s="58">
+      <c r="G25" s="61">
         <v>1</v>
       </c>
-      <c r="H25" s="92">
+      <c r="H25" s="98">
         <f>E25</f>
         <v>500000</v>
       </c>
-      <c r="I25" s="92"/>
+      <c r="I25" s="98"/>
       <c r="J25" s="36"/>
       <c r="K25" s="37"/>
     </row>
     <row r="26" spans="1:21" s="14" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A26" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="89"/>
+      <c r="A26" s="96" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="65"/>
       <c r="E26" s="33">
         <v>500000</v>
       </c>
       <c r="F26" s="34">
         <v>1</v>
       </c>
-      <c r="G26" s="58">
+      <c r="G26" s="61">
         <v>1</v>
       </c>
-      <c r="H26" s="92">
+      <c r="H26" s="98">
         <f t="shared" ref="H26" si="1">E26</f>
         <v>500000</v>
       </c>
-      <c r="I26" s="92"/>
+      <c r="I26" s="98"/>
       <c r="J26" s="36"/>
       <c r="K26" s="37"/>
     </row>
     <row r="27" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A27" s="87" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="88"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="89"/>
+      <c r="A27" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="65"/>
       <c r="E27" s="33">
         <v>2000000</v>
       </c>
       <c r="F27" s="34">
         <v>1</v>
       </c>
-      <c r="G27" s="58">
+      <c r="G27" s="61">
         <v>1</v>
       </c>
-      <c r="H27" s="92">
+      <c r="H27" s="98">
         <f>E27*F27*G27</f>
         <v>2000000</v>
       </c>
-      <c r="I27" s="92"/>
+      <c r="I27" s="98"/>
       <c r="J27" s="36"/>
       <c r="K27" s="37"/>
     </row>
     <row r="28" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="94" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="96"/>
+      <c r="A28" s="100" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="102"/>
       <c r="E28" s="33"/>
       <c r="F28" s="34"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="93">
+      <c r="G28" s="61"/>
+      <c r="H28" s="99">
         <f>SUM(H29:I30)</f>
         <v>4800000</v>
       </c>
-      <c r="I28" s="93"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="83"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="69"/>
     </row>
     <row r="29" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A29" s="87" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="88"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="89"/>
+      <c r="A29" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
       <c r="E29" s="33">
         <v>200000</v>
       </c>
       <c r="F29" s="34">
         <v>3</v>
       </c>
-      <c r="G29" s="58">
+      <c r="G29" s="61">
         <v>4</v>
       </c>
-      <c r="H29" s="92">
+      <c r="H29" s="98">
         <f>E29*F29*G29</f>
         <v>2400000</v>
       </c>
-      <c r="I29" s="92"/>
+      <c r="I29" s="98"/>
       <c r="J29" s="36"/>
       <c r="K29" s="37"/>
     </row>
     <row r="30" spans="1:21" s="14" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A30" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="89"/>
+      <c r="A30" s="96" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="65"/>
       <c r="E30" s="33">
         <v>200000</v>
       </c>
       <c r="F30" s="34">
         <v>3</v>
       </c>
-      <c r="G30" s="58">
+      <c r="G30" s="61">
         <v>4</v>
       </c>
-      <c r="H30" s="92">
+      <c r="H30" s="98">
         <f>E30*F30*G30</f>
         <v>2400000</v>
       </c>
-      <c r="I30" s="92"/>
+      <c r="I30" s="98"/>
       <c r="J30" s="36"/>
       <c r="K30" s="37"/>
     </row>
     <row r="31" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="65"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="64">
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="75">
         <f>H15+H28+H20+H24</f>
         <v>18000000</v>
       </c>
-      <c r="I31" s="64"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="81"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="92"/>
       <c r="L31" s="15"/>
       <c r="U31" s="38"/>
     </row>
     <row r="32" spans="1:21" s="14" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="62">
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="73">
         <f>H31*0.1</f>
         <v>1800000</v>
       </c>
-      <c r="I32" s="63"/>
+      <c r="I32" s="74"/>
       <c r="J32" s="39"/>
       <c r="K32" s="40"/>
       <c r="L32" s="15"/>
       <c r="P32" s="41"/>
     </row>
     <row r="33" spans="1:11" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="60">
+      <c r="B33" s="78"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="71">
         <f>SUM(H32,H31)</f>
         <v>19800000</v>
       </c>
-      <c r="I33" s="61"/>
+      <c r="I33" s="72"/>
       <c r="J33" s="42"/>
       <c r="K33" s="43"/>
     </row>
     <row r="34" spans="1:11" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="69"/>
-      <c r="C34" s="70"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="81"/>
       <c r="D34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3243,9 +3596,9 @@
       <c r="K34" s="47"/>
     </row>
     <row r="35" spans="1:11" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A35" s="71"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="73"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="83"/>
+      <c r="C35" s="84"/>
       <c r="D35" s="1" t="s">
         <v>12</v>
       </c>
@@ -3258,9 +3611,9 @@
       <c r="K35" s="18"/>
     </row>
     <row r="36" spans="1:11" s="14" customFormat="1" ht="22" customHeight="1">
-      <c r="A36" s="74"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="76"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="2" t="s">
         <v>13</v>
       </c>
@@ -3289,11 +3642,11 @@
       <c r="A38" s="11"/>
       <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
       <c r="H38" s="52" t="s">
         <v>23</v>
       </c>
@@ -3876,7 +4229,7 @@
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="H22:I22"/>
   </mergeCells>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{34685EC5-71D7-4B79-B482-9B7D5C49256D}"/>
   </hyperlinks>
